--- a/output/xlsx/CRUDLaboratorios--GT-.xlsx
+++ b/output/xlsx/CRUDLaboratorios--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="54">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -92,7 +92,7 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>superAdmin: seleciona opcao 'Laboratories' no menu Settings</t>
+    <t>superAdmin: seleciona opção 'Laboratories' no menu Settings</t>
   </si>
   <si>
     <t/>
@@ -101,7 +101,7 @@
     <t>SYSTEM exibe lista de laboratórios</t>
   </si>
   <si>
-    <t>superAdmin: seleciona o botao 'Create Laboratories'</t>
+    <t>superAdmin: seleciona o botão 'Create Laboratories'</t>
   </si>
   <si>
     <t>SYSTEM exibe página com campos de cadastro de novo Laboratório</t>
@@ -110,22 +110,19 @@
     <t xml:space="preserve">superAdmin: preenche corretamente os campos 'Name', 'Country' e 'Description' e pressiona o botão 'Create' </t>
   </si>
   <si>
-    <t>SYSTEM exibe pagina com dados do novo Laboratório e mensagem que um novo entrada foi adicionado</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe lista de laboratorios</t>
+    <t>SYSTEM exibe página com dados do novo Laboratório e mensagem que um novo entrada foi adicionado</t>
   </si>
   <si>
     <t>superAdmin: clica no nome de um Laboratório</t>
   </si>
   <si>
-    <t>SYSTEM exibe dados do Laboratorio e lista de usuarios associados a este</t>
+    <t>SYSTEM exibe dados do Laboratório e lista de usuários associados a este</t>
   </si>
   <si>
     <t>superAdmin: clica no botão 'Cancel'</t>
   </si>
   <si>
-    <t>SYSTEM retorna a lista de laboratorios</t>
+    <t>SYSTEM retorna a lista de laboratórios</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -134,22 +131,22 @@
     <t>TC2</t>
   </si>
   <si>
-    <t>Alternative Flow 1: Campo fora da formatacao esperada, e.g, Country = xx</t>
+    <t>Alternative Flow 1: Campo fora da formatação esperada, e.g, Country = xx</t>
   </si>
   <si>
     <t xml:space="preserve">superAdmin: preenche incorretamente algum dos campos 'Name', 'Country' ou 'Description' e pressiona o botão 'Create' </t>
   </si>
   <si>
-    <t>SYSTEM exibe mensagem informando que os dados nao correspondem a formatação esperada</t>
+    <t>SYSTEM exibe mensagem informando que os dados não correspondem a formatação esperada</t>
   </si>
   <si>
     <t>TC3</t>
   </si>
   <si>
-    <t>Alternative Flow 2: Cancela criacao</t>
-  </si>
-  <si>
-    <t>superAdmin: cancela criacao</t>
+    <t>Alternative Flow 2: Cancela criação</t>
+  </si>
+  <si>
+    <t>superAdmin: cancela criação</t>
   </si>
   <si>
     <t>TC4</t>
@@ -158,25 +155,25 @@
     <t>Alternative Flow 3: Edita dados</t>
   </si>
   <si>
-    <t>superAdmin: clica no botao 'Edit'</t>
+    <t>superAdmin: clica no botão 'Edit'</t>
   </si>
   <si>
     <t>SYSTEM exibe campos do Laboratório com valores atuais que podem ser editados</t>
   </si>
   <si>
-    <t>superAdmin: preenche os novos valores e pressiona o botao 'Update</t>
+    <t>superAdmin: preenche os novos valores e pressiona o botão 'Update</t>
   </si>
   <si>
     <t>TC5</t>
   </si>
   <si>
-    <t>Alternative Flow 4: Nome de Laboratorio já existente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">superAdmin: preenche o campo 'Name' com um nome de laboratorio ja existente. Preenche corretamente os campos 'Country' e 'Description' e pressiona o botao 'Create' </t>
-  </si>
-  <si>
-    <t>SYSTEM exibe mensagem informando que ja existe laboratório cadastrado com esse nome</t>
+    <t>Alternative Flow 4: Nome de Laboratório já existente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">superAdmin: preenche o campo 'Name' com um nome de laboratório jã existente. Preenche corretamente os campos 'Country' e 'Description' e pressiona o botão 'Create' </t>
+  </si>
+  <si>
+    <t>SYSTEM exibe mensagem informando que já existe laboratório cadastrado com esse nome</t>
   </si>
 </sst>
 </file>
@@ -442,7 +439,7 @@
         <v>27</v>
       </c>
       <c r="D13" t="s" s="3">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s" s="3">
         <v>27</v>
@@ -456,13 +453,13 @@
         <v>5.0</v>
       </c>
       <c r="B14" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s" s="3">
         <v>34</v>
-      </c>
-      <c r="C14" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s" s="3">
-        <v>35</v>
       </c>
       <c r="E14" t="s" s="3">
         <v>27</v>
@@ -476,13 +473,13 @@
         <v>6.0</v>
       </c>
       <c r="B15" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s" s="3">
         <v>36</v>
-      </c>
-      <c r="C15" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D15" t="s" s="3">
-        <v>37</v>
       </c>
       <c r="E15" t="s" s="3">
         <v>27</v>
@@ -493,7 +490,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>27</v>
@@ -504,7 +501,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s" s="1">
         <v>13</v>
@@ -518,7 +515,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s" s="1">
         <v>17</v>
@@ -597,13 +594,13 @@
         <v>3.0</v>
       </c>
       <c r="B25" t="s" s="3">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D25" t="s" s="3">
         <v>41</v>
-      </c>
-      <c r="C25" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D25" t="s" s="3">
-        <v>42</v>
       </c>
       <c r="E25" t="s" s="3">
         <v>27</v>
@@ -643,7 +640,7 @@
         <v>27</v>
       </c>
       <c r="D27" t="s" s="3">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s" s="3">
         <v>27</v>
@@ -657,13 +654,13 @@
         <v>6.0</v>
       </c>
       <c r="B28" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s" s="3">
         <v>34</v>
-      </c>
-      <c r="C28" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D28" t="s" s="3">
-        <v>35</v>
       </c>
       <c r="E28" t="s" s="3">
         <v>27</v>
@@ -677,13 +674,13 @@
         <v>7.0</v>
       </c>
       <c r="B29" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s" s="3">
         <v>36</v>
-      </c>
-      <c r="C29" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D29" t="s" s="3">
-        <v>37</v>
       </c>
       <c r="E29" t="s" s="3">
         <v>27</v>
@@ -694,7 +691,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>27</v>
@@ -705,7 +702,7 @@
         <v>11</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s" s="1">
         <v>13</v>
@@ -719,7 +716,7 @@
         <v>15</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E34" t="s" s="1">
         <v>17</v>
@@ -798,7 +795,7 @@
         <v>3.0</v>
       </c>
       <c r="B39" t="s" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s" s="3">
         <v>27</v>
@@ -864,7 +861,7 @@
         <v>27</v>
       </c>
       <c r="D42" t="s" s="3">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E42" t="s" s="3">
         <v>27</v>
@@ -878,13 +875,13 @@
         <v>7.0</v>
       </c>
       <c r="B43" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C43" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D43" t="s" s="3">
         <v>34</v>
-      </c>
-      <c r="C43" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D43" t="s" s="3">
-        <v>35</v>
       </c>
       <c r="E43" t="s" s="3">
         <v>27</v>
@@ -898,13 +895,13 @@
         <v>8.0</v>
       </c>
       <c r="B44" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C44" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s" s="3">
         <v>36</v>
-      </c>
-      <c r="C44" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D44" t="s" s="3">
-        <v>37</v>
       </c>
       <c r="E44" t="s" s="3">
         <v>27</v>
@@ -915,7 +912,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>27</v>
@@ -926,7 +923,7 @@
         <v>11</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" t="s" s="1">
         <v>13</v>
@@ -940,7 +937,7 @@
         <v>15</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E49" t="s" s="1">
         <v>17</v>
@@ -1045,7 +1042,7 @@
         <v>27</v>
       </c>
       <c r="D55" t="s" s="3">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E55" t="s" s="3">
         <v>27</v>
@@ -1059,13 +1056,13 @@
         <v>5.0</v>
       </c>
       <c r="B56" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C56" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D56" t="s" s="3">
         <v>34</v>
-      </c>
-      <c r="C56" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D56" t="s" s="3">
-        <v>35</v>
       </c>
       <c r="E56" t="s" s="3">
         <v>27</v>
@@ -1079,13 +1076,13 @@
         <v>6.0</v>
       </c>
       <c r="B57" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="C57" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D57" t="s" s="3">
         <v>48</v>
-      </c>
-      <c r="C57" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D57" t="s" s="3">
-        <v>49</v>
       </c>
       <c r="E57" t="s" s="3">
         <v>27</v>
@@ -1099,7 +1096,7 @@
         <v>7.0</v>
       </c>
       <c r="B58" t="s" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C58" t="s" s="3">
         <v>27</v>
@@ -1165,7 +1162,7 @@
         <v>27</v>
       </c>
       <c r="D61" t="s" s="3">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E61" t="s" s="3">
         <v>27</v>
@@ -1179,13 +1176,13 @@
         <v>11.0</v>
       </c>
       <c r="B62" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C62" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D62" t="s" s="3">
         <v>34</v>
-      </c>
-      <c r="C62" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D62" t="s" s="3">
-        <v>35</v>
       </c>
       <c r="E62" t="s" s="3">
         <v>27</v>
@@ -1199,13 +1196,13 @@
         <v>12.0</v>
       </c>
       <c r="B63" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C63" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D63" t="s" s="3">
         <v>36</v>
-      </c>
-      <c r="C63" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D63" t="s" s="3">
-        <v>37</v>
       </c>
       <c r="E63" t="s" s="3">
         <v>27</v>
@@ -1216,7 +1213,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B64" t="s" s="0">
         <v>27</v>
@@ -1227,7 +1224,7 @@
         <v>11</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C67" t="s" s="1">
         <v>13</v>
@@ -1241,7 +1238,7 @@
         <v>15</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E68" t="s" s="1">
         <v>17</v>
@@ -1320,13 +1317,13 @@
         <v>3.0</v>
       </c>
       <c r="B73" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="C73" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D73" t="s" s="3">
         <v>53</v>
-      </c>
-      <c r="C73" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D73" t="s" s="3">
-        <v>54</v>
       </c>
       <c r="E73" t="s" s="3">
         <v>27</v>
@@ -1366,7 +1363,7 @@
         <v>27</v>
       </c>
       <c r="D75" t="s" s="3">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E75" t="s" s="3">
         <v>27</v>
@@ -1380,13 +1377,13 @@
         <v>6.0</v>
       </c>
       <c r="B76" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C76" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D76" t="s" s="3">
         <v>34</v>
-      </c>
-      <c r="C76" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D76" t="s" s="3">
-        <v>35</v>
       </c>
       <c r="E76" t="s" s="3">
         <v>27</v>
@@ -1400,13 +1397,13 @@
         <v>7.0</v>
       </c>
       <c r="B77" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C77" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D77" t="s" s="3">
         <v>36</v>
-      </c>
-      <c r="C77" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D77" t="s" s="3">
-        <v>37</v>
       </c>
       <c r="E77" t="s" s="3">
         <v>27</v>
@@ -1417,7 +1414,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B78" t="s" s="0">
         <v>27</v>

--- a/output/xlsx/CRUDLaboratorios--GT-.xlsx
+++ b/output/xlsx/CRUDLaboratorios--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="59">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 5 test case(s)</t>
+    <t>Size: 6 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -101,7 +101,7 @@
     <t>SYSTEM exibe lista de laboratórios</t>
   </si>
   <si>
-    <t>superAdmin: seleciona o botão 'Create Laboratories'</t>
+    <t>superAdmin: seleciona o botão 'Create Laboratories', situado no lado direito inferior da tela</t>
   </si>
   <si>
     <t>SYSTEM exibe página com campos de cadastro de novo Laboratório</t>
@@ -167,7 +167,22 @@
     <t>TC5</t>
   </si>
   <si>
-    <t>Alternative Flow 4: Nome de Laboratório já existente</t>
+    <t>Alternative Flow 4: Deleta Laboratório</t>
+  </si>
+  <si>
+    <t>superAdmin: clica no botão 'Delete'</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe mensagem solicitando confirmação</t>
+  </si>
+  <si>
+    <t>superAdmin: pressiona o botao OK</t>
+  </si>
+  <si>
+    <t>TC6</t>
+  </si>
+  <si>
+    <t>Alternative Flow 5: Nome de Laboratório já existente</t>
   </si>
   <si>
     <t xml:space="preserve">superAdmin: preenche o campo 'Name' com um nome de laboratório jã existente. Preenche corretamente os campos 'Country' e 'Description' e pressiona o botão 'Create' </t>
@@ -265,7 +280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -1317,13 +1332,13 @@
         <v>3.0</v>
       </c>
       <c r="B73" t="s" s="3">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C73" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D73" t="s" s="3">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E73" t="s" s="3">
         <v>27</v>
@@ -1337,13 +1352,13 @@
         <v>4.0</v>
       </c>
       <c r="B74" t="s" s="3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D74" t="s" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E74" t="s" s="3">
         <v>27</v>
@@ -1357,13 +1372,13 @@
         <v>5.0</v>
       </c>
       <c r="B75" t="s" s="3">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C75" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D75" t="s" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E75" t="s" s="3">
         <v>27</v>
@@ -1377,13 +1392,13 @@
         <v>6.0</v>
       </c>
       <c r="B76" t="s" s="3">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C76" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D76" t="s" s="3">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E76" t="s" s="3">
         <v>27</v>
@@ -1397,26 +1412,327 @@
         <v>7.0</v>
       </c>
       <c r="B77" t="s" s="3">
+        <v>54</v>
+      </c>
+      <c r="C77" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D77" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E77" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F77" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="B78" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C78" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D78" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E78" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F78" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="B79" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C79" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D79" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E79" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F79" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="B80" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C80" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D80" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E80" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F80" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="B81" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C81" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D81" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E81" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F81" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="B82" t="s" s="3">
         <v>35</v>
       </c>
-      <c r="C77" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D77" t="s" s="3">
+      <c r="C82" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D82" t="s" s="3">
         <v>36</v>
       </c>
-      <c r="E77" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F77" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="1">
+      <c r="E82" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F82" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="B78" t="s" s="0">
+      <c r="B83" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C86" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E87" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D89" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E89" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F89" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B90" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D90" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E90" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F90" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B91" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C91" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D91" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E91" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F91" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B92" t="s" s="3">
+        <v>57</v>
+      </c>
+      <c r="C92" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D92" t="s" s="3">
+        <v>58</v>
+      </c>
+      <c r="E92" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F92" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B93" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C93" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D93" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E93" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F93" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B94" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C94" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D94" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E94" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F94" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B95" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C95" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D95" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E95" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F95" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B96" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C96" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D96" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="E96" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F96" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B97" t="s" s="0">
         <v>27</v>
       </c>
     </row>
